--- a/survey_templates/049_restaurant_customer_satisfaction_survey--survey_templates.xlsx
+++ b/survey_templates/049_restaurant_customer_satisfaction_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'rating_value_option_1',_'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 'rating_value_option_1', 'label': 'Very likely'}</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'rating_value_option_2',_'label':_'likely'}</t>
+          <t>likely</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 'rating_value_option_2', 'label': 'Likely'}</t>
+          <t>Likely</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'rating_value_option_3',_'label':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 'rating_value_option_3', 'label': 'Not likely'}</t>
+          <t>Not likely</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'reason_option_1',_'label':_'to_dine_in'}</t>
+          <t>to_dine_in</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 'reason_option_1', 'label': 'To dine in'}</t>
+          <t>To dine in</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'reason_option_2',_'label':_'to_take_an_order'}</t>
+          <t>to_take_an_order</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 'reason_option_2', 'label': 'To take an order'}</t>
+          <t>To take an order</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'reason_option_3',_'label':_'to_meet_a_friend'}</t>
+          <t>to_meet_a_friend</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 'reason_option_3', 'label': 'To meet a friend'}</t>
+          <t>To meet a friend</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'satisfaction_option_1',_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 'satisfaction_option_1', 'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'satisfaction_option_2',_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 'satisfaction_option_2', 'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'satisfaction_option_3',_'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 'satisfaction_option_3', 'label': 'Not satisfied'}</t>
+          <t>Not satisfied</t>
         </is>
       </c>
     </row>
